--- a/ds_0120.xlsx
+++ b/ds_0120.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C90E25-1868-4BE8-816D-375A757BF8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D58C7F-27DF-4A3A-8C5D-EB8F37559D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5145" yWindow="3135" windowWidth="22170" windowHeight="10650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="data" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">data!$A$1:$G$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">data!$A$1:$G$33</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="170">
   <si>
     <t>รหัสชุดข้อมูลตามที่กำหนดใน</t>
   </si>
@@ -519,9 +519,6 @@
   </si>
   <si>
     <t>อว 0652.38</t>
-  </si>
-  <si>
-    <t>ไม่ระบุ</t>
   </si>
   <si>
     <t>romyakon.l@rmutp.ac.th</t>
@@ -977,7 +974,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4254,7 +4251,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
@@ -4645,7 +4642,7 @@
         <v>122</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F17" s="13" t="s">
         <v>123</v>
@@ -4777,16 +4774,16 @@
         <v>22</v>
       </c>
       <c r="C23" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="E23" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="F23" s="13" t="s">
         <v>167</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>168</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>63</v>
@@ -4892,7 +4889,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>160</v>
@@ -4905,29 +4902,6 @@
       </c>
       <c r="G28" s="13" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="12.75">
-      <c r="A29" s="13">
-        <v>28</v>
-      </c>
-      <c r="B29" s="13">
-        <v>99</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
